--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_product_card.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_product_card.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>8.5</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>
